--- a/audio_ficition/books/excel/book-zh.xlsx
+++ b/audio_ficition/books/excel/book-zh.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,18 +448,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3cb86557-7add-4b3e-901a-eddf39815438</t>
+          <t>0dc4bec2-e970-4267-81f5-71693f3851e2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-06-30 23:14:04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>400f5353-1dfa-4baa-b9a5-c3c461e3430b</t>
+          <t>24ae0e5d-9b52-4494-9455-35b19fc44049</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -470,7 +474,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>431e6db4-df7a-4523-80f2-7db18fc0763d</t>
+          <t>2ceb92c5-c928-45d8-b890-5ae9e03b5119</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -481,7 +485,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4323841c-6bd3-406e-b7f5-ac29cb791c1c</t>
+          <t>350bb7ab-0470-49e1-97be-d95fff3044f7</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -492,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4e555ca7-5e1a-4a68-95f3-cacc37a0ba01</t>
+          <t>3ed6ef2d-7f63-4da1-acb9-901796b60b74</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -503,7 +507,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>720f6531-bdf2-4c83-9957-0e2c2376d4c0</t>
+          <t>5f23927e-e500-4804-8a00-b70a6cd65ec6</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -514,7 +518,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8abf7642-f23d-4da4-a2c9-9d3a062e9460</t>
+          <t>724c832c-bc78-429d-8fc5-04aa83db9c89</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -525,7 +529,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8f9b8311-3892-46d1-bae9-b062e9dcd28f</t>
+          <t>736522cc-f32d-4c0f-9c9d-d2c4ef6b1476</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -536,7 +540,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9aa2e5b4-fe5a-434c-a036-eb6d37c96cbc</t>
+          <t>9c56784e-28e3-4741-915c-18d120ef456d</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -547,7 +551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aaa9a6b2-e054-4eca-86d2-7fed52191e4d</t>
+          <t>9e796dbe-a250-4d32-9625-567cb2eb38f3</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -558,7 +562,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ad7acc5e-98c0-49a1-a733-d6a362ca2512</t>
+          <t>b6946244-69fe-4d47-bed0-4147f57c461b</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -569,7 +573,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b98c82e7-9bf0-4ad0-9fe5-0583956587ce</t>
+          <t>b8dc8a08-9fc5-45e9-9ed8-d8697cc55bf6</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -580,7 +584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>be6a7585-9e2f-469f-b037-fdfb1be4c9cf</t>
+          <t>bc3fc3f9-4746-49f3-a714-efc43d1799e0</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -591,13 +595,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>d59f7c5e-e4a8-4119-ab2b-24f7e69d7d53</t>
+          <t>d6aa432f-76ee-45b1-be1e-a39a0f14a114</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dbb30461-a314-4850-9b22-f6c7a599cd35</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dbe55589-7481-4587-9ba7-abfde7734b30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ef9c920f-c6a4-45b4-bede-87ddc2de01f9</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>f230cdb7-6c39-491e-bb5e-f2a695fff5b5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>f5a9a5e9-a204-41ee-994e-f1b067d95ddf</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/audio_ficition/books/excel/book-zh.xlsx
+++ b/audio_ficition/books/excel/book-zh.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-06-30 23:14:04</t>
+          <t>2025-07-01 12:41:25</t>
         </is>
       </c>
     </row>
@@ -467,9 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -478,9 +482,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-07-02 12:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -489,9 +497,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -500,9 +512,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-07-03 12:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -511,9 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,9 +542,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-07-04 12:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -533,9 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-07-05 00:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -544,9 +572,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-07-05 12:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -555,9 +587,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-07-06 00:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -566,9 +602,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-07-06 12:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -577,9 +617,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -588,9 +632,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-07-07 12:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/audio_ficition/books/excel/book-zh.xlsx
+++ b/audio_ficition/books/excel/book-zh.xlsx
@@ -625,9 +625,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>45854.42877314815</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -636,9 +638,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>45855.42877314815</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -647,9 +651,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>45856.42877314815</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -658,9 +664,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>45857.42877314815</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -669,9 +677,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>45858.42877314815</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -680,9 +690,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>45859.42877314815</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/audio_ficition/books/excel/book-zh.xlsx
+++ b/audio_ficition/books/excel/book-zh.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,234 +465,443 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24ae0e5d-9b52-4494-9455-35b19fc44049</t>
+          <t>1bc12a48-36e1-4db2-8ea0-01237920b32e</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>45841.48543981482</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2ceb92c5-c928-45d8-b890-5ae9e03b5119</t>
+          <t>1da05845-ad59-4bde-9c80-6566ced74d1d</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>45841.98543981482</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>350bb7ab-0470-49e1-97be-d95fff3044f7</t>
+          <t>24ae0e5d-9b52-4494-9455-35b19fc44049</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45842.48543981482</v>
+        <v>45841.48543981482</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3ed6ef2d-7f63-4da1-acb9-901796b60b74</t>
+          <t>2ceb92c5-c928-45d8-b890-5ae9e03b5119</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45842.98543981482</v>
+        <v>45841.98543981482</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f23927e-e500-4804-8a00-b70a6cd65ec6</t>
+          <t>3032119d-bbf6-4fd5-bd9d-8cb84866f0c4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>45843.48543981482</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>724c832c-bc78-429d-8fc5-04aa83db9c89</t>
+          <t>350bb7ab-0470-49e1-97be-d95fff3044f7</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45846.48543981482</v>
+        <v>45842.48543981482</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>736522cc-f32d-4c0f-9c9d-d2c4ef6b1476</t>
+          <t>3788599b-76ed-42f8-9383-10741650715d</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>45848.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9c56784e-28e3-4741-915c-18d120ef456d</t>
+          <t>3ed6ef2d-7f63-4da1-acb9-901796b60b74</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45849.42877314815</v>
+        <v>45842.98543981482</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9e796dbe-a250-4d32-9625-567cb2eb38f3</t>
+          <t>40c050dd-583b-4c80-8441-e7f579f839c6</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>45850.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b6946244-69fe-4d47-bed0-4147f57c461b</t>
+          <t>42593df4-dd63-4365-b854-1368c357e675</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>45851.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b8dc8a08-9fc5-45e9-9ed8-d8697cc55bf6</t>
+          <t>45113314-015a-4fdf-b5b2-62c2426e646c</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>45852.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bc3fc3f9-4746-49f3-a714-efc43d1799e0</t>
+          <t>4695d2a0-29b0-4cdf-bbc4-e30e20d30068</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>45853.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>d6aa432f-76ee-45b1-be1e-a39a0f14a114</t>
+          <t>52b8dea9-36f2-4e11-ac9f-6fdb0f5cc178</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>45854.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dbb30461-a314-4850-9b22-f6c7a599cd35</t>
+          <t>56bf073c-9aa5-43d2-866e-e32fdfe886b7</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>45855.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dbe55589-7481-4587-9ba7-abfde7734b30</t>
+          <t>5f23927e-e500-4804-8a00-b70a6cd65ec6</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>45856.42877314815</v>
+        <v>45843.48543981482</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ef9c920f-c6a4-45b4-bede-87ddc2de01f9</t>
+          <t>630c2762-a1ff-4284-acf6-268826bb2445</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>45857.42877314815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f230cdb7-6c39-491e-bb5e-f2a695fff5b5</t>
+          <t>724c832c-bc78-429d-8fc5-04aa83db9c89</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>45858.42877314815</v>
+        <v>45846.48543981482</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>736522cc-f32d-4c0f-9c9d-d2c4ef6b1476</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>45848.42877314815</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>765624b6-3c00-40c6-aa33-93d8a30dd1b6</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>77905a02-a273-4efa-932d-c9fb3f396c22</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>83a7e370-b35f-4a56-9c35-d5f6e25479fb</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8aafe530-6c68-4c6e-a757-3255ee05bd04</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>9c56784e-28e3-4741-915c-18d120ef456d</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>45849.42877314815</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>9e796dbe-a250-4d32-9625-567cb2eb38f3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>45850.42877314815</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aef4cd17-5e74-4fc2-bddb-8ac8296af0ef</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>b6946244-69fe-4d47-bed0-4147f57c461b</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>45851.42877314815</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>b8dc8a08-9fc5-45e9-9ed8-d8697cc55bf6</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>45852.42877314815</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bc3fc3f9-4746-49f3-a714-efc43d1799e0</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>45853.42877314815</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bcef560f-2230-44fe-b20f-5ff89ae62785</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>d2b8eae4-2e78-4136-82ce-7742dfe13aa0</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>d6aa432f-76ee-45b1-be1e-a39a0f14a114</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>45854.42877314815</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dbb30461-a314-4850-9b22-f6c7a599cd35</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>45855.42877314815</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dbe55589-7481-4587-9ba7-abfde7734b30</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>45856.42877314815</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>e9b94bb7-43ba-4f6a-9f59-e1d3d8e763a3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ef9c920f-c6a4-45b4-bede-87ddc2de01f9</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>45857.42877314815</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>f230cdb7-6c39-491e-bb5e-f2a695fff5b5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>45858.42877314815</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>f5a9a5e9-a204-41ee-994e-f1b067d95ddf</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2" t="n">
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="n">
         <v>45859.42877314815</v>
       </c>
     </row>

--- a/audio_ficition/books/excel/book-zh.xlsx
+++ b/audio_ficition/books/excel/book-zh.xlsx
@@ -469,9 +469,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>45860.42877314815</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -480,9 +482,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>45861.42877314815</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,9 +521,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>45862.42877314815</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -541,9 +547,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>45863.42877314815</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -565,9 +573,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>45864.42877314815</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -576,9 +586,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45865.42877314815</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,9 +599,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>45866.42877314815</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -598,9 +612,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>45867.42877314815</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -609,9 +625,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>45868.42877314815</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -620,9 +638,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>45869.42877314815</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -644,9 +664,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>45870.42877314815</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -681,9 +703,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>45871.42877314815</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -692,9 +716,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>45872.42877314815</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -703,9 +729,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>45873.42877314815</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -714,9 +742,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>45874.42877314815</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -751,9 +781,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>45875.42877314815</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -801,9 +833,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>45876.42877314815</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -812,9 +846,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>45877.42877314815</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -862,9 +898,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>45878.42877314815</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
